--- a/data/books/books.xlsx
+++ b/data/books/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ksnyder/Sites/public-domain-books/data/books/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FFEC02-DC5D-AA4A-B2DA-D973FC98D2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3A640C-E01D-6E47-A86C-FDD14437A158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1840" yWindow="500" windowWidth="47220" windowHeight="25960" xr2:uid="{948352A4-4516-F447-8F65-D2A52CDFF619}"/>
   </bookViews>
